--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2838-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2838-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C369E93-9FD0-4E16-8338-F0BCC31BE74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{863E2155-4BD5-4A01-B668-D7CDD13E320D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{BF2D2FA1-07F5-4C74-A8C2-3965805A8B9B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{1960D5A5-4625-4B7F-9328-46BF855F9481}"/>
   </bookViews>
   <sheets>
     <sheet name="2838-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1469,24 +1469,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E18B2780-7B0F-4106-9C77-2E7216C39CA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{080A7ED3-FCCB-41E8-AABF-E6B9A7D9F14F}">
   <dimension ref="A1:R46"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1514,7 +1514,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1544,7 +1544,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1640,7 +1640,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41">
         <v>2024</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2023</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="41">
         <v>2022</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>26</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>26</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="39">
         <v>2021</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="41">
         <v>2020</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>26</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="39">
         <v>2019</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>5.86</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2410,7 +2410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>26</v>
       </c>
@@ -2466,7 +2466,7 @@
         <v>5.86</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="41">
         <v>2018</v>
       </c>
@@ -2520,7 +2520,7 @@
         <v>6.51</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2017</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>4.82</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="41">
         <v>2016</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>4.54</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2015</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>8.31</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="41">
         <v>2014</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39">
         <v>2013</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="41">
         <v>2012</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>2011</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="41">
         <v>2010</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>2009</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="41">
         <v>2008</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2007</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="41">
         <v>2006</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="39">
         <v>2005</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="41">
         <v>2004</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="39">
         <v>2003</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="41">
         <v>2002</v>
       </c>
@@ -3384,7 +3384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>2001</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="41">
         <v>2000</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="39">
         <v>1999</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>4.7699999999999996</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="41">
         <v>1998</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="39">
         <v>1997</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="41">
         <v>1996</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="39">
         <v>1995</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="41">
         <v>1994</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="39">
         <v>1993</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="41" t="s">
         <v>40</v>
       </c>
